--- a/StructureDefinition-base-stroke-observation.xlsx
+++ b/StructureDefinition-base-stroke-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T10:04:33+00:00</t>
+    <t>2026-02-09T10:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-base-stroke-observation.xlsx
+++ b/StructureDefinition-base-stroke-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="493">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T10:35:12+00:00</t>
+    <t>2026-10-27T13:25:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1325,6 +1325,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>value:IVL_PQ.low</t>
@@ -7220,7 +7224,7 @@
         <v>414</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>415</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7235,7 +7239,7 @@
         <v>405</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>20</v>
@@ -7243,10 +7247,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7272,10 +7276,10 @@
         <v>411</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7326,7 +7330,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7338,7 +7342,7 @@
         <v>414</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>415</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7353,7 +7357,7 @@
         <v>405</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>20</v>
@@ -7361,10 +7365,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7390,10 +7394,10 @@
         <v>234</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7423,10 +7427,10 @@
         <v>330</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7444,7 +7448,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7471,7 +7475,7 @@
         <v>405</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>20</v>
@@ -7479,10 +7483,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7508,16 +7512,16 @@
         <v>234</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7545,10 +7549,10 @@
         <v>239</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7566,7 +7570,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7587,10 +7591,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>345</v>
@@ -7601,10 +7605,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7630,16 +7634,16 @@
         <v>234</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7667,10 +7671,10 @@
         <v>250</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7688,7 +7692,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7709,10 +7713,10 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>345</v>
@@ -7723,10 +7727,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7749,17 +7753,17 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7808,7 +7812,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7835,7 +7839,7 @@
         <v>20</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>20</v>
@@ -7843,10 +7847,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7869,13 +7873,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7926,7 +7930,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7953,7 +7957,7 @@
         <v>405</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>20</v>
@@ -7961,10 +7965,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7987,16 +7991,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8046,7 +8050,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8070,7 +8074,7 @@
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>200</v>
@@ -8081,10 +8085,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8107,16 +8111,16 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8166,7 +8170,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8190,10 +8194,10 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>20</v>
@@ -8201,10 +8205,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8230,16 +8234,16 @@
         <v>178</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8288,7 +8292,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8312,10 +8316,10 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>20</v>
@@ -8323,10 +8327,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8441,10 +8445,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8561,10 +8565,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8683,10 +8687,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8712,13 +8716,13 @@
         <v>234</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>249</v>
@@ -8770,7 +8774,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>93</v>
@@ -8791,7 +8795,7 @@
         <v>255</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>257</v>
@@ -8805,10 +8809,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8834,13 +8838,13 @@
         <v>315</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M58" t="s" s="2">
         <v>317</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>319</v>
@@ -8892,7 +8896,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8913,7 +8917,7 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>322</v>
@@ -8927,10 +8931,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8956,13 +8960,13 @@
         <v>234</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>329</v>
@@ -9014,7 +9018,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9049,10 +9053,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9136,7 +9140,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9171,10 +9175,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9200,10 +9204,10 @@
         <v>82</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>402</v>
@@ -9258,7 +9262,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>

--- a/StructureDefinition-base-stroke-observation.xlsx
+++ b/StructureDefinition-base-stroke-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:25:43+00:00</t>
+    <t>2026-10-27T13:28:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
